--- a/data/nzd0461/nzd0461.xlsx
+++ b/data/nzd0461/nzd0461.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N356"/>
+  <dimension ref="A1:N357"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17430,7 +17430,7 @@
         </is>
       </c>
       <c r="B356" t="n">
-        <v>435.8</v>
+        <v>433.73</v>
       </c>
       <c r="C356" t="n">
         <v>424.21</v>
@@ -17466,6 +17466,54 @@
         <v>402.31</v>
       </c>
       <c r="N356" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-11 22:26:24+00:00</t>
+        </is>
+      </c>
+      <c r="B357" t="n">
+        <v>405.81</v>
+      </c>
+      <c r="C357" t="n">
+        <v>400.76</v>
+      </c>
+      <c r="D357" t="n">
+        <v>414.96</v>
+      </c>
+      <c r="E357" t="n">
+        <v>434.07</v>
+      </c>
+      <c r="F357" t="n">
+        <v>423.27</v>
+      </c>
+      <c r="G357" t="n">
+        <v>408.14</v>
+      </c>
+      <c r="H357" t="n">
+        <v>396.2</v>
+      </c>
+      <c r="I357" t="n">
+        <v>392.61</v>
+      </c>
+      <c r="J357" t="n">
+        <v>383.47</v>
+      </c>
+      <c r="K357" t="n">
+        <v>381.3</v>
+      </c>
+      <c r="L357" t="n">
+        <v>392.09</v>
+      </c>
+      <c r="M357" t="n">
+        <v>395.1</v>
+      </c>
+      <c r="N357" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -17482,7 +17530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B371"/>
+  <dimension ref="A1:B372"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21195,6 +21243,16 @@
       </c>
       <c r="B371" t="n">
         <v>0.86</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>2026-09-11 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B372" t="n">
+        <v>0.89</v>
       </c>
     </row>
   </sheetData>
@@ -21363,28 +21421,28 @@
         <v>0.1696</v>
       </c>
       <c r="I2" t="n">
-        <v>1.103586339747733</v>
+        <v>1.109388299768209</v>
       </c>
       <c r="J2" t="n">
+        <v>356</v>
+      </c>
+      <c r="K2" t="n">
         <v>355</v>
       </c>
-      <c r="K2" t="n">
-        <v>354</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.1590975715537959</v>
+        <v>0.1613946652227869</v>
       </c>
       <c r="M2" t="n">
-        <v>16.12806110667361</v>
+        <v>16.10679439098901</v>
       </c>
       <c r="N2" t="n">
-        <v>378.3971821694295</v>
+        <v>377.276925247643</v>
       </c>
       <c r="O2" t="n">
-        <v>19.45243383665472</v>
+        <v>19.42361771781053</v>
       </c>
       <c r="P2" t="n">
-        <v>363.5714599096686</v>
+        <v>363.5115213768512</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -21445,28 +21503,28 @@
         <v>0.1201</v>
       </c>
       <c r="I3" t="n">
-        <v>1.225646383336688</v>
+        <v>1.233689169273286</v>
       </c>
       <c r="J3" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K3" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1913934354063518</v>
+        <v>0.1941813387567112</v>
       </c>
       <c r="M3" t="n">
-        <v>16.07937508579271</v>
+        <v>16.06906150850406</v>
       </c>
       <c r="N3" t="n">
-        <v>372.25203229932</v>
+        <v>371.7972166293067</v>
       </c>
       <c r="O3" t="n">
-        <v>19.29383404871411</v>
+        <v>19.28204389138524</v>
       </c>
       <c r="P3" t="n">
-        <v>353.143527703456</v>
+        <v>353.0606413441559</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -21527,28 +21585,28 @@
         <v>0.1062</v>
       </c>
       <c r="I4" t="n">
-        <v>1.439806415235286</v>
+        <v>1.454668105932103</v>
       </c>
       <c r="J4" t="n">
+        <v>356</v>
+      </c>
+      <c r="K4" t="n">
         <v>355</v>
       </c>
-      <c r="K4" t="n">
-        <v>354</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.2617892392266437</v>
+        <v>0.2658816215097655</v>
       </c>
       <c r="M4" t="n">
-        <v>15.75354593878933</v>
+        <v>15.77319554432663</v>
       </c>
       <c r="N4" t="n">
-        <v>342.6914427767931</v>
+        <v>343.7438668615115</v>
       </c>
       <c r="O4" t="n">
-        <v>18.51192704114818</v>
+        <v>18.54033081855638</v>
       </c>
       <c r="P4" t="n">
-        <v>349.2466698420923</v>
+        <v>349.0932731144518</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -21609,28 +21667,28 @@
         <v>0.1328</v>
       </c>
       <c r="I5" t="n">
-        <v>1.344165279002858</v>
+        <v>1.365896280113115</v>
       </c>
       <c r="J5" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K5" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2397783161444066</v>
+        <v>0.2444946523029917</v>
       </c>
       <c r="M5" t="n">
-        <v>15.55692960244687</v>
+        <v>15.60220815745754</v>
       </c>
       <c r="N5" t="n">
-        <v>337.0190463891713</v>
+        <v>340.3893153915874</v>
       </c>
       <c r="O5" t="n">
-        <v>18.35807850482101</v>
+        <v>18.44964269007905</v>
       </c>
       <c r="P5" t="n">
-        <v>358.6167074515587</v>
+        <v>358.3924851140263</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -21691,28 +21749,28 @@
         <v>0.1398</v>
       </c>
       <c r="I6" t="n">
-        <v>1.385436435939511</v>
+        <v>1.397160811480943</v>
       </c>
       <c r="J6" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K6" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2691155311301365</v>
+        <v>0.272900264250644</v>
       </c>
       <c r="M6" t="n">
-        <v>14.70531737922563</v>
+        <v>14.71056885619027</v>
       </c>
       <c r="N6" t="n">
-        <v>306.5345328090553</v>
+        <v>306.9212444799625</v>
       </c>
       <c r="O6" t="n">
-        <v>17.50812762145214</v>
+        <v>17.51916791631276</v>
       </c>
       <c r="P6" t="n">
-        <v>364.7874427612865</v>
+        <v>364.6662834795072</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -21769,28 +21827,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>1.356323992218319</v>
+        <v>1.366015830312751</v>
       </c>
       <c r="J7" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K7" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L7" t="n">
-        <v>0.258345150708469</v>
+        <v>0.2617818892161716</v>
       </c>
       <c r="M7" t="n">
-        <v>15.2700176525968</v>
+        <v>15.26671686156436</v>
       </c>
       <c r="N7" t="n">
-        <v>309.8449590064523</v>
+        <v>309.8257890689049</v>
       </c>
       <c r="O7" t="n">
-        <v>17.60241344266326</v>
+        <v>17.60186890841154</v>
       </c>
       <c r="P7" t="n">
-        <v>354.0799432024726</v>
+        <v>353.9796225724846</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -21847,28 +21905,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>1.351955535933768</v>
+        <v>1.358647285028869</v>
       </c>
       <c r="J8" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K8" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2498651183069911</v>
+        <v>0.2526947892805618</v>
       </c>
       <c r="M8" t="n">
-        <v>15.87844450200921</v>
+        <v>15.85966115831333</v>
       </c>
       <c r="N8" t="n">
-        <v>323.6566576496236</v>
+        <v>323.150280062645</v>
       </c>
       <c r="O8" t="n">
-        <v>17.99046018448732</v>
+        <v>17.97638117260103</v>
       </c>
       <c r="P8" t="n">
-        <v>347.654485403319</v>
+        <v>347.5856922480471</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -21925,28 +21983,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>1.388319214011521</v>
+        <v>1.395247315853785</v>
       </c>
       <c r="J9" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K9" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2558269478488925</v>
+        <v>0.258704698074077</v>
       </c>
       <c r="M9" t="n">
-        <v>16.02408237568848</v>
+        <v>16.00677623501621</v>
       </c>
       <c r="N9" t="n">
-        <v>330.7797950091673</v>
+        <v>330.2827665513923</v>
       </c>
       <c r="O9" t="n">
-        <v>18.18735261133866</v>
+        <v>18.173683351247</v>
       </c>
       <c r="P9" t="n">
-        <v>342.6516186949169</v>
+        <v>342.5804145823523</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -22003,28 +22061,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>1.50733039585152</v>
+        <v>1.512155213776252</v>
       </c>
       <c r="J10" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K10" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2873637618426432</v>
+        <v>0.2898631776334609</v>
       </c>
       <c r="M10" t="n">
-        <v>15.91158933379585</v>
+        <v>15.88595014648834</v>
       </c>
       <c r="N10" t="n">
-        <v>334.1514776604964</v>
+        <v>333.414370295284</v>
       </c>
       <c r="O10" t="n">
-        <v>18.27981065712926</v>
+        <v>18.25963773724123</v>
       </c>
       <c r="P10" t="n">
-        <v>334.1035730022701</v>
+        <v>334.0540785399229</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -22081,28 +22139,28 @@
         <v>0.1806</v>
       </c>
       <c r="I11" t="n">
-        <v>1.511209419217505</v>
+        <v>1.515254463814313</v>
       </c>
       <c r="J11" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K11" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2816402259106832</v>
+        <v>0.2839427591754228</v>
       </c>
       <c r="M11" t="n">
-        <v>15.90340542762609</v>
+        <v>15.87442531257177</v>
       </c>
       <c r="N11" t="n">
-        <v>342.7745276700243</v>
+        <v>341.9557232516352</v>
       </c>
       <c r="O11" t="n">
-        <v>18.51417099602422</v>
+        <v>18.49204486398503</v>
       </c>
       <c r="P11" t="n">
-        <v>333.2459717163012</v>
+        <v>333.2043603191664</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -22159,28 +22217,28 @@
         <v>0.1692</v>
       </c>
       <c r="I12" t="n">
-        <v>1.309636455597546</v>
+        <v>1.315453998958049</v>
       </c>
       <c r="J12" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K12" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2603067551331849</v>
+        <v>0.263053819147382</v>
       </c>
       <c r="M12" t="n">
-        <v>14.55863391768401</v>
+        <v>14.54043406467557</v>
       </c>
       <c r="N12" t="n">
-        <v>287.381697579466</v>
+        <v>286.8777742899543</v>
       </c>
       <c r="O12" t="n">
-        <v>16.95233605080627</v>
+        <v>16.93746658417233</v>
       </c>
       <c r="P12" t="n">
-        <v>346.2664186928449</v>
+        <v>346.2065953309592</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -22237,28 +22295,28 @@
         <v>0.1283</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7525040179990771</v>
+        <v>0.7591484090096885</v>
       </c>
       <c r="J13" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K13" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L13" t="n">
-        <v>0.138775929739529</v>
+        <v>0.1414310326646485</v>
       </c>
       <c r="M13" t="n">
-        <v>12.37317758766518</v>
+        <v>12.36464097544617</v>
       </c>
       <c r="N13" t="n">
-        <v>206.0965346297055</v>
+        <v>205.9128747880391</v>
       </c>
       <c r="O13" t="n">
-        <v>14.35606264369536</v>
+        <v>14.34966462284186</v>
       </c>
       <c r="P13" t="n">
-        <v>362.854497822433</v>
+        <v>362.78569489877</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -22296,7 +22354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N356"/>
+  <dimension ref="A1:N357"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47723,7 +47781,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>-44.40579617122986,167.91798189127337</t>
+          <t>-44.40581036945228,167.9179986491486</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -47782,6 +47840,78 @@
         </is>
       </c>
       <c r="N356" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-11 22:26:24+00:00</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>-44.406001873772595,167.91822467886075</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>-44.405602018827395,167.9189266654953</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>-44.40507012517657,167.9194728109496</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>-44.40452175562084,167.9199507903658</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>-44.404234772161594,167.9205217414272</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>-44.40381355019494,167.9209876929646</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>-44.4032840574414,167.9215058923858</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>-44.40273555918378,167.92191937162147</t>
+        </is>
+      </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>-44.40218879304467,167.92232856751005</t>
+        </is>
+      </c>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>-44.40159442362413,167.9226479602488</t>
+        </is>
+      </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>-44.40097797345623,167.9228049540038</t>
+        </is>
+      </c>
+      <c r="M357" t="inlineStr">
+        <is>
+          <t>-44.40037315852682,167.9229455730128</t>
+        </is>
+      </c>
+      <c r="N357" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
